--- a/public/deviceExcel/gateway.xlsx
+++ b/public/deviceExcel/gateway.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>网关名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -24,179 +24,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20210328000002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20210328000003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20210328000004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20210328000005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20210328000006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20210328000007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20210328000008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20210328000009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试2</t>
-  </si>
-  <si>
-    <t>测试3</t>
-  </si>
-  <si>
-    <t>测试4</t>
-  </si>
-  <si>
-    <t>测试5</t>
-  </si>
-  <si>
-    <t>测试6</t>
-  </si>
-  <si>
-    <t>测试7</t>
-  </si>
-  <si>
-    <t>测试8</t>
-  </si>
-  <si>
-    <t>测试9</t>
-  </si>
-  <si>
-    <t>ZTWLPB02</t>
-  </si>
-  <si>
-    <t>ZTWLPB03</t>
-  </si>
-  <si>
-    <t>ZTWLPB04</t>
-  </si>
-  <si>
-    <t>ZTWLPB05</t>
-  </si>
-  <si>
-    <t>ZTWLPB06</t>
-  </si>
-  <si>
-    <t>ZTWLPB07</t>
-  </si>
-  <si>
-    <t>ZTWLPB08</t>
-  </si>
-  <si>
-    <t>ZTWLPB09</t>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>地上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网关备注1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网关备注2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网关备注3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网关备注4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网关备注5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网关备注6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网关备注7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网关备注8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网关备注9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20210113323</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
     <t>心跳周期(秒)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZTWLPB01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -576,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
@@ -588,235 +416,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
